--- a/results/Compact/Results_Compact.xlsx
+++ b/results/Compact/Results_Compact.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lenz/Downloads/Results_Compact_100.xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lenz/Documents/GitHub/columngeneration_consistency/results/Compact/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB3AF72-6E94-114C-9D47-B742AB6919D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51EB80B0-1AF4-8549-91B9-9B24CDE1A393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3171,7 +3171,7 @@
         <v>1598.18</v>
       </c>
       <c r="M62">
-        <v>8.4000000000000005E-2</v>
+        <v>0.13400000000000001</v>
       </c>
       <c r="N62">
         <v>9</v>
@@ -3391,7 +3391,7 @@
         <v>1538.06</v>
       </c>
       <c r="M67">
-        <v>9.5000000000000001E-2</v>
+        <v>0.123</v>
       </c>
       <c r="N67">
         <v>9</v>
@@ -5503,7 +5503,7 @@
         <v>799.94</v>
       </c>
       <c r="M115">
-        <v>0.10299999999999999</v>
+        <v>0.123</v>
       </c>
       <c r="N115">
         <v>9</v>
@@ -5811,7 +5811,7 @@
         <v>886.94</v>
       </c>
       <c r="M122">
-        <v>0.17899999999999999</v>
+        <v>0.19900000000000001</v>
       </c>
       <c r="N122">
         <v>9</v>
@@ -5943,7 +5943,7 @@
         <v>951.7</v>
       </c>
       <c r="M125">
-        <v>0.111</v>
+        <v>0.13</v>
       </c>
       <c r="N125">
         <v>9</v>
@@ -5987,7 +5987,7 @@
         <v>771.88</v>
       </c>
       <c r="M126">
-        <v>0.122</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="N126">
         <v>9</v>
@@ -6031,7 +6031,7 @@
         <v>1238.0999999999999</v>
       </c>
       <c r="M127">
-        <v>7.5999999999999998E-2</v>
+        <v>0.106</v>
       </c>
       <c r="N127">
         <v>9</v>
@@ -6075,7 +6075,7 @@
         <v>1136.06</v>
       </c>
       <c r="M128">
-        <v>4.5999999999999999E-2</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="N128">
         <v>9</v>
@@ -6427,7 +6427,7 @@
         <v>1270.02</v>
       </c>
       <c r="M136">
-        <v>7.0000000000000007E-2</v>
+        <v>0.12</v>
       </c>
       <c r="N136">
         <v>9</v>
@@ -6471,7 +6471,7 @@
         <v>1045.1400000000001</v>
       </c>
       <c r="M137">
-        <v>0.08</v>
+        <v>0.122</v>
       </c>
       <c r="N137">
         <v>9</v>
@@ -6603,7 +6603,7 @@
         <v>1067.94</v>
       </c>
       <c r="M140">
-        <v>6.3E-2</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="N140">
         <v>9</v>
@@ -6647,7 +6647,7 @@
         <v>1221.1199999999999</v>
       </c>
       <c r="M141">
-        <v>8.6999999999999994E-2</v>
+        <v>0.1087</v>
       </c>
       <c r="N141">
         <v>9</v>
@@ -6691,7 +6691,7 @@
         <v>978.96</v>
       </c>
       <c r="M142">
-        <v>5.7000000000000002E-2</v>
+        <v>0.107</v>
       </c>
       <c r="N142">
         <v>9</v>
@@ -6779,7 +6779,7 @@
         <v>1101.52</v>
       </c>
       <c r="M144">
-        <v>4.4999999999999998E-2</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="N144">
         <v>9</v>
@@ -6955,7 +6955,7 @@
         <v>1128.04</v>
       </c>
       <c r="M148">
-        <v>6.6000000000000003E-2</v>
+        <v>0.126</v>
       </c>
       <c r="N148">
         <v>9</v>
@@ -6999,7 +6999,7 @@
         <v>1117.28</v>
       </c>
       <c r="M149">
-        <v>7.8E-2</v>
+        <v>0.123</v>
       </c>
       <c r="N149">
         <v>9</v>
@@ -7043,7 +7043,7 @@
         <v>1214.96</v>
       </c>
       <c r="M150">
-        <v>6.3E-2</v>
+        <v>0.10630000000000001</v>
       </c>
       <c r="N150">
         <v>9</v>
@@ -7263,7 +7263,7 @@
         <v>318.64</v>
       </c>
       <c r="M155">
-        <v>0.22500000000000001</v>
+        <v>0.23200000000000001</v>
       </c>
       <c r="N155">
         <v>9</v>
@@ -7395,7 +7395,7 @@
         <v>266.33999999999997</v>
       </c>
       <c r="M158">
-        <v>0.24</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="N158">
         <v>9</v>
@@ -7483,7 +7483,7 @@
         <v>345.34</v>
       </c>
       <c r="M160">
-        <v>0.17699999999999999</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="N160">
         <v>9</v>

--- a/results/Compact/Results_Compact.xlsx
+++ b/results/Compact/Results_Compact.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lenz/Documents/GitHub/columngeneration_consistency/results/Compact/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lenz/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51EB80B0-1AF4-8549-91B9-9B24CDE1A393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E849E7D3-AEAF-A245-9405-2AEA3056C463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -102,6 +102,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -446,10 +447,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N226"/>
+  <dimension ref="A1:P226"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -493,7 +494,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>150</v>
       </c>
@@ -531,13 +532,18 @@
         <v>1033.48</v>
       </c>
       <c r="M2">
+        <f>ROUND((I2-J2)/I2,3)</f>
         <v>0.38900000000000001</v>
       </c>
       <c r="N2">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="P2">
+        <f>MIN(M2:M226)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>150</v>
       </c>
@@ -575,13 +581,14 @@
         <v>1034.48</v>
       </c>
       <c r="M3">
+        <f t="shared" ref="M3:M66" si="0">ROUND((I3-J3)/I3,3)</f>
         <v>0.25900000000000001</v>
       </c>
       <c r="N3">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>150</v>
       </c>
@@ -619,13 +626,14 @@
         <v>1218.02</v>
       </c>
       <c r="M4">
+        <f t="shared" si="0"/>
         <v>0.34100000000000003</v>
       </c>
       <c r="N4">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>150</v>
       </c>
@@ -663,13 +671,14 @@
         <v>1105.68</v>
       </c>
       <c r="M5">
+        <f t="shared" si="0"/>
         <v>0.313</v>
       </c>
       <c r="N5">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>150</v>
       </c>
@@ -707,13 +716,14 @@
         <v>1167.04</v>
       </c>
       <c r="M6">
+        <f t="shared" si="0"/>
         <v>0.37</v>
       </c>
       <c r="N6">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>150</v>
       </c>
@@ -751,13 +761,14 @@
         <v>1148.56</v>
       </c>
       <c r="M7">
+        <f t="shared" si="0"/>
         <v>0.34100000000000003</v>
       </c>
       <c r="N7">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>150</v>
       </c>
@@ -795,13 +806,14 @@
         <v>1086.5999999999999</v>
       </c>
       <c r="M8">
+        <f t="shared" si="0"/>
         <v>0.437</v>
       </c>
       <c r="N8">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>150</v>
       </c>
@@ -839,13 +851,14 @@
         <v>1216.18</v>
       </c>
       <c r="M9">
+        <f t="shared" si="0"/>
         <v>0.40300000000000002</v>
       </c>
       <c r="N9">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>150</v>
       </c>
@@ -883,13 +896,14 @@
         <v>1213.44</v>
       </c>
       <c r="M10">
+        <f t="shared" si="0"/>
         <v>0.26700000000000002</v>
       </c>
       <c r="N10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>150</v>
       </c>
@@ -927,13 +941,14 @@
         <v>1265.98</v>
       </c>
       <c r="M11">
+        <f t="shared" si="0"/>
         <v>0.29299999999999998</v>
       </c>
       <c r="N11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>150</v>
       </c>
@@ -971,13 +986,14 @@
         <v>1048.02</v>
       </c>
       <c r="M12">
+        <f t="shared" si="0"/>
         <v>0.377</v>
       </c>
       <c r="N12">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>150</v>
       </c>
@@ -1015,13 +1031,14 @@
         <v>945.04</v>
       </c>
       <c r="M13">
+        <f t="shared" si="0"/>
         <v>0.45300000000000001</v>
       </c>
       <c r="N13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>150</v>
       </c>
@@ -1059,13 +1076,14 @@
         <v>1108.4000000000001</v>
       </c>
       <c r="M14">
+        <f t="shared" si="0"/>
         <v>0.33600000000000002</v>
       </c>
       <c r="N14">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>150</v>
       </c>
@@ -1103,13 +1121,14 @@
         <v>957.96</v>
       </c>
       <c r="M15">
+        <f t="shared" si="0"/>
         <v>0.316</v>
       </c>
       <c r="N15">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>150</v>
       </c>
@@ -1147,6 +1166,7 @@
         <v>1229.68</v>
       </c>
       <c r="M16">
+        <f t="shared" si="0"/>
         <v>0.32100000000000001</v>
       </c>
       <c r="N16">
@@ -1191,6 +1211,7 @@
         <v>966.24</v>
       </c>
       <c r="M17">
+        <f t="shared" si="0"/>
         <v>0.42199999999999999</v>
       </c>
       <c r="N17">
@@ -1235,6 +1256,7 @@
         <v>1214.76</v>
       </c>
       <c r="M18">
+        <f t="shared" si="0"/>
         <v>0.314</v>
       </c>
       <c r="N18">
@@ -1279,6 +1301,7 @@
         <v>1001.68</v>
       </c>
       <c r="M19">
+        <f t="shared" si="0"/>
         <v>0.27700000000000002</v>
       </c>
       <c r="N19">
@@ -1323,6 +1346,7 @@
         <v>968.36</v>
       </c>
       <c r="M20">
+        <f t="shared" si="0"/>
         <v>0.38600000000000001</v>
       </c>
       <c r="N20">
@@ -1367,6 +1391,7 @@
         <v>1015.22</v>
       </c>
       <c r="M21">
+        <f t="shared" si="0"/>
         <v>0.34699999999999998</v>
       </c>
       <c r="N21">
@@ -1411,6 +1436,7 @@
         <v>1121.98</v>
       </c>
       <c r="M22">
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="N22">
@@ -1455,6 +1481,7 @@
         <v>1049.98</v>
       </c>
       <c r="M23">
+        <f t="shared" si="0"/>
         <v>0.307</v>
       </c>
       <c r="N23">
@@ -1499,6 +1526,7 @@
         <v>1026.46</v>
       </c>
       <c r="M24">
+        <f t="shared" si="0"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="N24">
@@ -1543,6 +1571,7 @@
         <v>1224.98</v>
       </c>
       <c r="M25">
+        <f t="shared" si="0"/>
         <v>0.308</v>
       </c>
       <c r="N25">
@@ -1587,6 +1616,7 @@
         <v>1010.5</v>
       </c>
       <c r="M26">
+        <f t="shared" si="0"/>
         <v>0.39900000000000002</v>
       </c>
       <c r="N26">
@@ -1631,6 +1661,7 @@
         <v>1348.68</v>
       </c>
       <c r="M27">
+        <f t="shared" si="0"/>
         <v>0.22700000000000001</v>
       </c>
       <c r="N27">
@@ -1675,6 +1706,7 @@
         <v>1453.4</v>
       </c>
       <c r="M28">
+        <f t="shared" si="0"/>
         <v>0.16700000000000001</v>
       </c>
       <c r="N28">
@@ -1719,6 +1751,7 @@
         <v>1560.68</v>
       </c>
       <c r="M29">
+        <f t="shared" si="0"/>
         <v>0.21299999999999999</v>
       </c>
       <c r="N29">
@@ -1763,6 +1796,7 @@
         <v>1484.64</v>
       </c>
       <c r="M30">
+        <f t="shared" si="0"/>
         <v>0.19800000000000001</v>
       </c>
       <c r="N30">
@@ -1807,6 +1841,7 @@
         <v>1489.08</v>
       </c>
       <c r="M31">
+        <f t="shared" si="0"/>
         <v>0.23</v>
       </c>
       <c r="N31">
@@ -1851,6 +1886,7 @@
         <v>1457.4</v>
       </c>
       <c r="M32">
+        <f t="shared" si="0"/>
         <v>0.193</v>
       </c>
       <c r="N32">
@@ -1895,6 +1931,7 @@
         <v>1367.08</v>
       </c>
       <c r="M33">
+        <f t="shared" si="0"/>
         <v>0.27900000000000003</v>
       </c>
       <c r="N33">
@@ -1939,6 +1976,7 @@
         <v>1589.26</v>
       </c>
       <c r="M34">
+        <f t="shared" si="0"/>
         <v>0.25800000000000001</v>
       </c>
       <c r="N34">
@@ -1983,6 +2021,7 @@
         <v>1627</v>
       </c>
       <c r="M35">
+        <f t="shared" si="0"/>
         <v>0.19700000000000001</v>
       </c>
       <c r="N35">
@@ -2015,7 +2054,7 @@
         <v>3</v>
       </c>
       <c r="I36">
-        <v>1528.6</v>
+        <v>1628.6</v>
       </c>
       <c r="J36">
         <v>1344.6</v>
@@ -2027,7 +2066,8 @@
         <v>1528.6</v>
       </c>
       <c r="M36">
-        <v>0.12</v>
+        <f t="shared" si="0"/>
+        <v>0.17399999999999999</v>
       </c>
       <c r="N36">
         <v>9</v>
@@ -2071,6 +2111,7 @@
         <v>1296.1600000000001</v>
       </c>
       <c r="M37">
+        <f t="shared" si="0"/>
         <v>0.189</v>
       </c>
       <c r="N37">
@@ -2115,6 +2156,7 @@
         <v>1155.72</v>
       </c>
       <c r="M38">
+        <f t="shared" si="0"/>
         <v>0.221</v>
       </c>
       <c r="N38">
@@ -2159,6 +2201,7 @@
         <v>1491.12</v>
       </c>
       <c r="M39">
+        <f t="shared" si="0"/>
         <v>0.21199999999999999</v>
       </c>
       <c r="N39">
@@ -2203,6 +2246,7 @@
         <v>1360.22</v>
       </c>
       <c r="M40">
+        <f t="shared" si="0"/>
         <v>0.20100000000000001</v>
       </c>
       <c r="N40">
@@ -2247,6 +2291,7 @@
         <v>1555.38</v>
       </c>
       <c r="M41">
+        <f t="shared" si="0"/>
         <v>0.192</v>
       </c>
       <c r="N41">
@@ -2291,6 +2336,7 @@
         <v>1232.54</v>
       </c>
       <c r="M42">
+        <f t="shared" si="0"/>
         <v>0.21099999999999999</v>
       </c>
       <c r="N42">
@@ -2335,6 +2381,7 @@
         <v>1536.74</v>
       </c>
       <c r="M43">
+        <f t="shared" si="0"/>
         <v>0.17499999999999999</v>
       </c>
       <c r="N43">
@@ -2367,7 +2414,7 @@
         <v>3</v>
       </c>
       <c r="I44">
-        <v>1372.04</v>
+        <v>1392.04</v>
       </c>
       <c r="J44">
         <v>1179.4000000000001</v>
@@ -2379,7 +2426,8 @@
         <v>1372.04</v>
       </c>
       <c r="M44">
-        <v>0.14000000000000001</v>
+        <f t="shared" si="0"/>
+        <v>0.153</v>
       </c>
       <c r="N44">
         <v>9</v>
@@ -2423,6 +2471,7 @@
         <v>1346.72</v>
       </c>
       <c r="M45">
+        <f t="shared" si="0"/>
         <v>0.22600000000000001</v>
       </c>
       <c r="N45">
@@ -2455,7 +2504,7 @@
         <v>3</v>
       </c>
       <c r="I46">
-        <v>1238.08</v>
+        <v>1278.08</v>
       </c>
       <c r="J46">
         <v>1060.441</v>
@@ -2467,7 +2516,8 @@
         <v>1238.08</v>
       </c>
       <c r="M46">
-        <v>0.14299999999999999</v>
+        <f t="shared" si="0"/>
+        <v>0.17</v>
       </c>
       <c r="N46">
         <v>9</v>
@@ -2511,6 +2561,7 @@
         <v>1447.16</v>
       </c>
       <c r="M47">
+        <f t="shared" si="0"/>
         <v>0.251</v>
       </c>
       <c r="N47">
@@ -2555,6 +2606,7 @@
         <v>1436.44</v>
       </c>
       <c r="M48">
+        <f t="shared" si="0"/>
         <v>0.19</v>
       </c>
       <c r="N48">
@@ -2599,6 +2651,7 @@
         <v>1397.06</v>
       </c>
       <c r="M49">
+        <f t="shared" si="0"/>
         <v>0.19</v>
       </c>
       <c r="N49">
@@ -2643,6 +2696,7 @@
         <v>1584.08</v>
       </c>
       <c r="M50">
+        <f t="shared" si="0"/>
         <v>0.19400000000000001</v>
       </c>
       <c r="N50">
@@ -2687,6 +2741,7 @@
         <v>1374.24</v>
       </c>
       <c r="M51">
+        <f t="shared" si="0"/>
         <v>0.25600000000000001</v>
       </c>
       <c r="N51">
@@ -2731,6 +2786,7 @@
         <v>1695.22</v>
       </c>
       <c r="M52">
+        <f t="shared" si="0"/>
         <v>0.159</v>
       </c>
       <c r="N52">
@@ -2763,7 +2819,7 @@
         <v>3</v>
       </c>
       <c r="I53">
-        <v>1801.68</v>
+        <v>2001.68</v>
       </c>
       <c r="J53">
         <v>1646.68</v>
@@ -2775,7 +2831,8 @@
         <v>1801.68</v>
       </c>
       <c r="M53">
-        <v>8.5999999999999993E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.17699999999999999</v>
       </c>
       <c r="N53">
         <v>9</v>
@@ -2819,6 +2876,7 @@
         <v>1907.74</v>
       </c>
       <c r="M54">
+        <f t="shared" si="0"/>
         <v>0.13100000000000001</v>
       </c>
       <c r="N54">
@@ -2851,7 +2909,7 @@
         <v>3</v>
       </c>
       <c r="I55">
-        <v>1809.04</v>
+        <v>1929.04</v>
       </c>
       <c r="J55">
         <v>1634.64</v>
@@ -2863,7 +2921,8 @@
         <v>1809.04</v>
       </c>
       <c r="M55">
-        <v>9.6000000000000002E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.153</v>
       </c>
       <c r="N55">
         <v>9</v>
@@ -2907,6 +2966,7 @@
         <v>1830.42</v>
       </c>
       <c r="M56">
+        <f t="shared" si="0"/>
         <v>0.13500000000000001</v>
       </c>
       <c r="N56">
@@ -2951,6 +3011,7 @@
         <v>1835.52</v>
       </c>
       <c r="M57">
+        <f t="shared" si="0"/>
         <v>0.12</v>
       </c>
       <c r="N57">
@@ -2995,6 +3056,7 @@
         <v>1676.34</v>
       </c>
       <c r="M58">
+        <f t="shared" si="0"/>
         <v>0.158</v>
       </c>
       <c r="N58">
@@ -3039,6 +3101,7 @@
         <v>1934.58</v>
       </c>
       <c r="M59">
+        <f t="shared" si="0"/>
         <v>0.17299999999999999</v>
       </c>
       <c r="N59">
@@ -3083,6 +3146,7 @@
         <v>1981.12</v>
       </c>
       <c r="M60">
+        <f t="shared" si="0"/>
         <v>0.123</v>
       </c>
       <c r="N60">
@@ -3115,7 +3179,7 @@
         <v>3</v>
       </c>
       <c r="I61">
-        <v>1928.5</v>
+        <v>1998.5</v>
       </c>
       <c r="J61">
         <v>1784.12</v>
@@ -3127,7 +3191,8 @@
         <v>1928.5</v>
       </c>
       <c r="M61">
-        <v>7.4999999999999997E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.107</v>
       </c>
       <c r="N61">
         <v>9</v>
@@ -3159,7 +3224,7 @@
         <v>3</v>
       </c>
       <c r="I62">
-        <v>1598.18</v>
+        <v>1698.18</v>
       </c>
       <c r="J62">
         <v>1464.5</v>
@@ -3171,7 +3236,8 @@
         <v>1598.18</v>
       </c>
       <c r="M62">
-        <v>0.13400000000000001</v>
+        <f t="shared" si="0"/>
+        <v>0.13800000000000001</v>
       </c>
       <c r="N62">
         <v>9</v>
@@ -3215,6 +3281,7 @@
         <v>1567.16</v>
       </c>
       <c r="M63">
+        <f t="shared" si="0"/>
         <v>0.16200000000000001</v>
       </c>
       <c r="N63">
@@ -3259,6 +3326,7 @@
         <v>1834.52</v>
       </c>
       <c r="M64">
+        <f t="shared" si="0"/>
         <v>0.122</v>
       </c>
       <c r="N64">
@@ -3291,7 +3359,7 @@
         <v>3</v>
       </c>
       <c r="I65">
-        <v>1701.5</v>
+        <v>1781.5</v>
       </c>
       <c r="J65">
         <v>1513.78</v>
@@ -3303,7 +3371,8 @@
         <v>1701.5</v>
       </c>
       <c r="M65">
-        <v>0.11</v>
+        <f t="shared" si="0"/>
+        <v>0.15</v>
       </c>
       <c r="N65">
         <v>9</v>
@@ -3347,6 +3416,7 @@
         <v>1921.4</v>
       </c>
       <c r="M66">
+        <f t="shared" si="0"/>
         <v>0.13</v>
       </c>
       <c r="N66">
@@ -3379,7 +3449,7 @@
         <v>3</v>
       </c>
       <c r="I67">
-        <v>1538.06</v>
+        <v>1578.06</v>
       </c>
       <c r="J67">
         <v>1391.42</v>
@@ -3391,7 +3461,8 @@
         <v>1538.06</v>
       </c>
       <c r="M67">
-        <v>0.123</v>
+        <f t="shared" ref="M67:M130" si="1">ROUND((I67-J67)/I67,3)</f>
+        <v>0.11799999999999999</v>
       </c>
       <c r="N67">
         <v>9</v>
@@ -3435,6 +3506,7 @@
         <v>1961.42</v>
       </c>
       <c r="M68">
+        <f t="shared" si="1"/>
         <v>0.13100000000000001</v>
       </c>
       <c r="N68">
@@ -3467,7 +3539,7 @@
         <v>3</v>
       </c>
       <c r="I69">
-        <v>1714.88</v>
+        <v>1764.88</v>
       </c>
       <c r="J69">
         <v>1582.48</v>
@@ -3479,7 +3551,8 @@
         <v>1714.88</v>
       </c>
       <c r="M69">
-        <v>7.6999999999999999E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.10299999999999999</v>
       </c>
       <c r="N69">
         <v>9</v>
@@ -3523,6 +3596,7 @@
         <v>1707.78</v>
       </c>
       <c r="M70">
+        <f t="shared" si="1"/>
         <v>0.14099999999999999</v>
       </c>
       <c r="N70">
@@ -3567,6 +3641,7 @@
         <v>1654.1</v>
       </c>
       <c r="M71">
+        <f t="shared" si="1"/>
         <v>0.108</v>
       </c>
       <c r="N71">
@@ -3611,6 +3686,7 @@
         <v>1820.88</v>
       </c>
       <c r="M72">
+        <f t="shared" si="1"/>
         <v>0.16500000000000001</v>
       </c>
       <c r="N72">
@@ -3655,6 +3731,7 @@
         <v>1846.08</v>
       </c>
       <c r="M73">
+        <f t="shared" si="1"/>
         <v>0.13800000000000001</v>
       </c>
       <c r="N73">
@@ -3687,7 +3764,7 @@
         <v>3</v>
       </c>
       <c r="I74">
-        <v>1748.96</v>
+        <v>1799.96</v>
       </c>
       <c r="J74">
         <v>1561.06</v>
@@ -3699,7 +3776,8 @@
         <v>1748.96</v>
       </c>
       <c r="M74">
-        <v>0.107</v>
+        <f t="shared" si="1"/>
+        <v>0.13300000000000001</v>
       </c>
       <c r="N74">
         <v>9</v>
@@ -3743,6 +3821,7 @@
         <v>1970.62</v>
       </c>
       <c r="M75">
+        <f t="shared" si="1"/>
         <v>0.126</v>
       </c>
       <c r="N75">
@@ -3787,6 +3866,7 @@
         <v>1695.46</v>
       </c>
       <c r="M76">
+        <f t="shared" si="1"/>
         <v>0.156</v>
       </c>
       <c r="N76">
@@ -3831,6 +3911,7 @@
         <v>712.74</v>
       </c>
       <c r="M77">
+        <f t="shared" si="1"/>
         <v>0.17499999999999999</v>
       </c>
       <c r="N77">
@@ -3875,6 +3956,7 @@
         <v>623.38</v>
       </c>
       <c r="M78">
+        <f t="shared" si="1"/>
         <v>0.19</v>
       </c>
       <c r="N78">
@@ -3919,6 +4001,7 @@
         <v>733.34</v>
       </c>
       <c r="M79">
+        <f t="shared" si="1"/>
         <v>0.26100000000000001</v>
       </c>
       <c r="N79">
@@ -3963,6 +4046,7 @@
         <v>706.16</v>
       </c>
       <c r="M80">
+        <f t="shared" si="1"/>
         <v>0.27</v>
       </c>
       <c r="N80">
@@ -4007,6 +4091,7 @@
         <v>719.82</v>
       </c>
       <c r="M81">
+        <f t="shared" si="1"/>
         <v>0.315</v>
       </c>
       <c r="N81">
@@ -4051,6 +4136,7 @@
         <v>663.2</v>
       </c>
       <c r="M82">
+        <f t="shared" si="1"/>
         <v>0.23599999999999999</v>
       </c>
       <c r="N82">
@@ -4095,6 +4181,7 @@
         <v>637.17999999999995</v>
       </c>
       <c r="M83">
+        <f t="shared" si="1"/>
         <v>0.34899999999999998</v>
       </c>
       <c r="N83">
@@ -4139,6 +4226,7 @@
         <v>746.46</v>
       </c>
       <c r="M84">
+        <f t="shared" si="1"/>
         <v>0.33200000000000002</v>
       </c>
       <c r="N84">
@@ -4183,6 +4271,7 @@
         <v>736.86</v>
       </c>
       <c r="M85">
+        <f t="shared" si="1"/>
         <v>0.19500000000000001</v>
       </c>
       <c r="N85">
@@ -4227,6 +4316,7 @@
         <v>772.96</v>
       </c>
       <c r="M86">
+        <f t="shared" si="1"/>
         <v>0.222</v>
       </c>
       <c r="N86">
@@ -4271,6 +4361,7 @@
         <v>653.9</v>
       </c>
       <c r="M87">
+        <f t="shared" si="1"/>
         <v>0.314</v>
       </c>
       <c r="N87">
@@ -4315,6 +4406,7 @@
         <v>547.98</v>
       </c>
       <c r="M88">
+        <f t="shared" si="1"/>
         <v>0.36499999999999999</v>
       </c>
       <c r="N88">
@@ -4359,6 +4451,7 @@
         <v>680.08</v>
       </c>
       <c r="M89">
+        <f t="shared" si="1"/>
         <v>0.27900000000000003</v>
       </c>
       <c r="N89">
@@ -4403,6 +4496,7 @@
         <v>615.08000000000004</v>
       </c>
       <c r="M90">
+        <f t="shared" si="1"/>
         <v>0.29699999999999999</v>
       </c>
       <c r="N90">
@@ -4447,6 +4541,7 @@
         <v>713.2</v>
       </c>
       <c r="M91">
+        <f t="shared" si="1"/>
         <v>0.20499999999999999</v>
       </c>
       <c r="N91">
@@ -4491,6 +4586,7 @@
         <v>607.52</v>
       </c>
       <c r="M92">
+        <f t="shared" si="1"/>
         <v>0.38800000000000001</v>
       </c>
       <c r="N92">
@@ -4535,6 +4631,7 @@
         <v>761.1</v>
       </c>
       <c r="M93">
+        <f t="shared" si="1"/>
         <v>0.27200000000000002</v>
       </c>
       <c r="N93">
@@ -4579,6 +4676,7 @@
         <v>625.17999999999995</v>
       </c>
       <c r="M94">
+        <f t="shared" si="1"/>
         <v>0.23200000000000001</v>
       </c>
       <c r="N94">
@@ -4623,6 +4721,7 @@
         <v>592.26</v>
       </c>
       <c r="M95">
+        <f t="shared" si="1"/>
         <v>0.31900000000000001</v>
       </c>
       <c r="N95">
@@ -4667,6 +4766,7 @@
         <v>623.67999999999995</v>
       </c>
       <c r="M96">
+        <f t="shared" si="1"/>
         <v>0.29699999999999999</v>
       </c>
       <c r="N96">
@@ -4711,6 +4811,7 @@
         <v>661.76</v>
       </c>
       <c r="M97">
+        <f t="shared" si="1"/>
         <v>0.31</v>
       </c>
       <c r="N97">
@@ -4755,6 +4856,7 @@
         <v>669.7</v>
       </c>
       <c r="M98">
+        <f t="shared" si="1"/>
         <v>0.27300000000000002</v>
       </c>
       <c r="N98">
@@ -4799,6 +4901,7 @@
         <v>656.62</v>
       </c>
       <c r="M99">
+        <f t="shared" si="1"/>
         <v>0.255</v>
       </c>
       <c r="N99">
@@ -4843,6 +4946,7 @@
         <v>763.16</v>
       </c>
       <c r="M100">
+        <f t="shared" si="1"/>
         <v>0.25900000000000001</v>
       </c>
       <c r="N100">
@@ -4887,6 +4991,7 @@
         <v>612.1</v>
       </c>
       <c r="M101">
+        <f t="shared" si="1"/>
         <v>0.33700000000000002</v>
       </c>
       <c r="N101">
@@ -4931,6 +5036,7 @@
         <v>841.62</v>
       </c>
       <c r="M102">
+        <f t="shared" si="1"/>
         <v>0.128</v>
       </c>
       <c r="N102">
@@ -4963,7 +5069,7 @@
         <v>3</v>
       </c>
       <c r="I103">
-        <v>903.68</v>
+        <v>923.68</v>
       </c>
       <c r="J103">
         <v>802.8</v>
@@ -4975,7 +5081,8 @@
         <v>903.68</v>
       </c>
       <c r="M103">
-        <v>0.112</v>
+        <f t="shared" si="1"/>
+        <v>0.13100000000000001</v>
       </c>
       <c r="N103">
         <v>9</v>
@@ -5019,6 +5126,7 @@
         <v>972.26</v>
       </c>
       <c r="M104">
+        <f t="shared" si="1"/>
         <v>0.16300000000000001</v>
       </c>
       <c r="N104">
@@ -5063,6 +5171,7 @@
         <v>900.76</v>
       </c>
       <c r="M105">
+        <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
       <c r="N105">
@@ -5107,6 +5216,7 @@
         <v>926.3</v>
       </c>
       <c r="M106">
+        <f t="shared" si="1"/>
         <v>0.16800000000000001</v>
       </c>
       <c r="N106">
@@ -5151,6 +5261,7 @@
         <v>922.48</v>
       </c>
       <c r="M107">
+        <f t="shared" si="1"/>
         <v>0.14399999999999999</v>
       </c>
       <c r="N107">
@@ -5195,6 +5306,7 @@
         <v>853.86</v>
       </c>
       <c r="M108">
+        <f t="shared" si="1"/>
         <v>0.219</v>
       </c>
       <c r="N108">
@@ -5239,6 +5351,7 @@
         <v>1026</v>
       </c>
       <c r="M109">
+        <f t="shared" si="1"/>
         <v>0.23200000000000001</v>
       </c>
       <c r="N109">
@@ -5283,6 +5396,7 @@
         <v>1043.3800000000001</v>
       </c>
       <c r="M110">
+        <f t="shared" si="1"/>
         <v>0.16800000000000001</v>
       </c>
       <c r="N110">
@@ -5327,6 +5441,7 @@
         <v>1019.38</v>
       </c>
       <c r="M111">
+        <f t="shared" si="1"/>
         <v>0.124</v>
       </c>
       <c r="N111">
@@ -5371,6 +5486,7 @@
         <v>791.96</v>
       </c>
       <c r="M112">
+        <f t="shared" si="1"/>
         <v>0.11899999999999999</v>
       </c>
       <c r="N112">
@@ -5415,6 +5531,7 @@
         <v>751.16</v>
       </c>
       <c r="M113">
+        <f t="shared" si="1"/>
         <v>0.19900000000000001</v>
       </c>
       <c r="N113">
@@ -5447,7 +5564,7 @@
         <v>3</v>
       </c>
       <c r="I114">
-        <v>876.64</v>
+        <v>896.64</v>
       </c>
       <c r="J114">
         <v>781.3</v>
@@ -5459,7 +5576,8 @@
         <v>876.64</v>
       </c>
       <c r="M114">
-        <v>0.109</v>
+        <f t="shared" si="1"/>
+        <v>0.129</v>
       </c>
       <c r="N114">
         <v>9</v>
@@ -5491,7 +5609,7 @@
         <v>3</v>
       </c>
       <c r="I115">
-        <v>799.94</v>
+        <v>829.94</v>
       </c>
       <c r="J115">
         <v>717.62</v>
@@ -5503,7 +5621,8 @@
         <v>799.94</v>
       </c>
       <c r="M115">
-        <v>0.123</v>
+        <f t="shared" si="1"/>
+        <v>0.13500000000000001</v>
       </c>
       <c r="N115">
         <v>9</v>
@@ -5547,6 +5666,7 @@
         <v>962.76</v>
       </c>
       <c r="M116">
+        <f t="shared" si="1"/>
         <v>0.129</v>
       </c>
       <c r="N116">
@@ -5591,6 +5711,7 @@
         <v>803.36</v>
       </c>
       <c r="M117">
+        <f t="shared" si="1"/>
         <v>0.185</v>
       </c>
       <c r="N117">
@@ -5635,6 +5756,7 @@
         <v>985.84</v>
       </c>
       <c r="M118">
+        <f t="shared" si="1"/>
         <v>0.14899999999999999</v>
       </c>
       <c r="N118">
@@ -5667,7 +5789,7 @@
         <v>3</v>
       </c>
       <c r="I119">
-        <v>861.58</v>
+        <v>891.58</v>
       </c>
       <c r="J119">
         <v>776.38</v>
@@ -5679,7 +5801,8 @@
         <v>861.58</v>
       </c>
       <c r="M119">
-        <v>9.9000000000000005E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.129</v>
       </c>
       <c r="N119">
         <v>9</v>
@@ -5723,6 +5846,7 @@
         <v>788.22</v>
       </c>
       <c r="M120">
+        <f t="shared" si="1"/>
         <v>0.13200000000000001</v>
       </c>
       <c r="N120">
@@ -5767,6 +5891,7 @@
         <v>802.04</v>
       </c>
       <c r="M121">
+        <f t="shared" si="1"/>
         <v>0.121</v>
       </c>
       <c r="N121">
@@ -5811,7 +5936,8 @@
         <v>886.94</v>
       </c>
       <c r="M122">
-        <v>0.19900000000000001</v>
+        <f t="shared" si="1"/>
+        <v>0.17899999999999999</v>
       </c>
       <c r="N122">
         <v>9</v>
@@ -5855,6 +5981,7 @@
         <v>880.04</v>
       </c>
       <c r="M123">
+        <f t="shared" si="1"/>
         <v>0.127</v>
       </c>
       <c r="N123">
@@ -5899,6 +6026,7 @@
         <v>901.72</v>
       </c>
       <c r="M124">
+        <f t="shared" si="1"/>
         <v>0.159</v>
       </c>
       <c r="N124">
@@ -5931,7 +6059,7 @@
         <v>3</v>
       </c>
       <c r="I125">
-        <v>951.7</v>
+        <v>971.7</v>
       </c>
       <c r="J125">
         <v>846.18</v>
@@ -5943,7 +6071,8 @@
         <v>951.7</v>
       </c>
       <c r="M125">
-        <v>0.13</v>
+        <f t="shared" si="1"/>
+        <v>0.129</v>
       </c>
       <c r="N125">
         <v>9</v>
@@ -5987,7 +6116,8 @@
         <v>771.88</v>
       </c>
       <c r="M126">
-        <v>0.14199999999999999</v>
+        <f t="shared" si="1"/>
+        <v>0.122</v>
       </c>
       <c r="N126">
         <v>9</v>
@@ -6019,7 +6149,7 @@
         <v>3</v>
       </c>
       <c r="I127">
-        <v>1238.0999999999999</v>
+        <v>1338.1</v>
       </c>
       <c r="J127">
         <v>1144.28</v>
@@ -6031,7 +6161,8 @@
         <v>1238.0999999999999</v>
       </c>
       <c r="M127">
-        <v>0.106</v>
+        <f t="shared" si="1"/>
+        <v>0.14499999999999999</v>
       </c>
       <c r="N127">
         <v>9</v>
@@ -6063,7 +6194,7 @@
         <v>3</v>
       </c>
       <c r="I128">
-        <v>1136.06</v>
+        <v>1236.06</v>
       </c>
       <c r="J128">
         <v>1084.24</v>
@@ -6075,7 +6206,8 @@
         <v>1136.06</v>
       </c>
       <c r="M128">
-        <v>9.8000000000000004E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.123</v>
       </c>
       <c r="N128">
         <v>9</v>
@@ -6107,7 +6239,7 @@
         <v>3</v>
       </c>
       <c r="I129">
-        <v>1203.8399999999999</v>
+        <v>1353.84</v>
       </c>
       <c r="J129">
         <v>1098.3800000000001</v>
@@ -6119,7 +6251,8 @@
         <v>1203.8399999999999</v>
       </c>
       <c r="M129">
-        <v>8.7999999999999995E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.189</v>
       </c>
       <c r="N129">
         <v>9</v>
@@ -6151,7 +6284,7 @@
         <v>3</v>
       </c>
       <c r="I130">
-        <v>1151.54</v>
+        <v>1451.54</v>
       </c>
       <c r="J130">
         <v>1084.26</v>
@@ -6163,7 +6296,8 @@
         <v>1151.54</v>
       </c>
       <c r="M130">
-        <v>5.8000000000000003E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.253</v>
       </c>
       <c r="N130">
         <v>9</v>
@@ -6207,6 +6341,7 @@
         <v>1164.26</v>
       </c>
       <c r="M131">
+        <f t="shared" ref="M131:M194" si="2">ROUND((I131-J131)/I131,3)</f>
         <v>0.10199999999999999</v>
       </c>
       <c r="N131">
@@ -6239,7 +6374,7 @@
         <v>3</v>
       </c>
       <c r="I132">
-        <v>1154.02</v>
+        <v>1214.02</v>
       </c>
       <c r="J132">
         <v>1066.08</v>
@@ -6251,7 +6386,8 @@
         <v>1154.02</v>
       </c>
       <c r="M132">
-        <v>7.5999999999999998E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.122</v>
       </c>
       <c r="N132">
         <v>9</v>
@@ -6283,7 +6419,7 @@
         <v>3</v>
       </c>
       <c r="I133">
-        <v>1059.24</v>
+        <v>1099.24</v>
       </c>
       <c r="J133">
         <v>944.22</v>
@@ -6295,7 +6431,8 @@
         <v>1059.24</v>
       </c>
       <c r="M133">
-        <v>0.109</v>
+        <f t="shared" si="2"/>
+        <v>0.14099999999999999</v>
       </c>
       <c r="N133">
         <v>9</v>
@@ -6339,6 +6476,7 @@
         <v>1217.78</v>
       </c>
       <c r="M134">
+        <f t="shared" si="2"/>
         <v>0.126</v>
       </c>
       <c r="N134">
@@ -6371,7 +6509,7 @@
         <v>3</v>
       </c>
       <c r="I135">
-        <v>1254.0999999999999</v>
+        <v>1294.0999999999999</v>
       </c>
       <c r="J135">
         <v>1156.6199999999999</v>
@@ -6383,7 +6521,8 @@
         <v>1254.0999999999999</v>
       </c>
       <c r="M135">
-        <v>7.8E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.106</v>
       </c>
       <c r="N135">
         <v>9</v>
@@ -6415,7 +6554,7 @@
         <v>3</v>
       </c>
       <c r="I136">
-        <v>1270.02</v>
+        <v>1340.02</v>
       </c>
       <c r="J136">
         <v>1180.54</v>
@@ -6427,7 +6566,8 @@
         <v>1270.02</v>
       </c>
       <c r="M136">
-        <v>0.12</v>
+        <f t="shared" si="2"/>
+        <v>0.11899999999999999</v>
       </c>
       <c r="N136">
         <v>9</v>
@@ -6459,7 +6599,7 @@
         <v>3</v>
       </c>
       <c r="I137">
-        <v>1045.1400000000001</v>
+        <v>1145.1400000000001</v>
       </c>
       <c r="J137">
         <v>961.06</v>
@@ -6471,7 +6611,8 @@
         <v>1045.1400000000001</v>
       </c>
       <c r="M137">
-        <v>0.122</v>
+        <f t="shared" si="2"/>
+        <v>0.161</v>
       </c>
       <c r="N137">
         <v>9</v>
@@ -6503,7 +6644,7 @@
         <v>3</v>
       </c>
       <c r="I138">
-        <v>952.06</v>
+        <v>982.06</v>
       </c>
       <c r="J138">
         <v>869.32</v>
@@ -6515,7 +6656,8 @@
         <v>952.06</v>
       </c>
       <c r="M138">
-        <v>8.6999999999999994E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.115</v>
       </c>
       <c r="N138">
         <v>9</v>
@@ -6547,7 +6689,7 @@
         <v>3</v>
       </c>
       <c r="I139">
-        <v>1181.3800000000001</v>
+        <v>1201.3800000000001</v>
       </c>
       <c r="J139">
         <v>1067.24</v>
@@ -6559,7 +6701,8 @@
         <v>1181.3800000000001</v>
       </c>
       <c r="M139">
-        <v>9.7000000000000003E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.112</v>
       </c>
       <c r="N139">
         <v>9</v>
@@ -6591,7 +6734,7 @@
         <v>3</v>
       </c>
       <c r="I140">
-        <v>1067.94</v>
+        <v>1217.94</v>
       </c>
       <c r="J140">
         <v>1000.54</v>
@@ -6603,7 +6746,8 @@
         <v>1067.94</v>
       </c>
       <c r="M140">
-        <v>0.16300000000000001</v>
+        <f t="shared" si="2"/>
+        <v>0.17799999999999999</v>
       </c>
       <c r="N140">
         <v>9</v>
@@ -6635,7 +6779,7 @@
         <v>3</v>
       </c>
       <c r="I141">
-        <v>1221.1199999999999</v>
+        <v>1321.12</v>
       </c>
       <c r="J141">
         <v>1115.3599999999999</v>
@@ -6647,7 +6791,8 @@
         <v>1221.1199999999999</v>
       </c>
       <c r="M141">
-        <v>0.1087</v>
+        <f t="shared" si="2"/>
+        <v>0.156</v>
       </c>
       <c r="N141">
         <v>9</v>
@@ -6679,7 +6824,7 @@
         <v>3</v>
       </c>
       <c r="I142">
-        <v>978.96</v>
+        <v>1048.96</v>
       </c>
       <c r="J142">
         <v>922.78</v>
@@ -6691,7 +6836,8 @@
         <v>978.96</v>
       </c>
       <c r="M142">
-        <v>0.107</v>
+        <f t="shared" si="2"/>
+        <v>0.12</v>
       </c>
       <c r="N142">
         <v>9</v>
@@ -6723,7 +6869,7 @@
         <v>3</v>
       </c>
       <c r="I143">
-        <v>1247.18</v>
+        <v>1287.18</v>
       </c>
       <c r="J143">
         <v>1139.56</v>
@@ -6735,7 +6881,8 @@
         <v>1247.18</v>
       </c>
       <c r="M143">
-        <v>8.5999999999999993E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.115</v>
       </c>
       <c r="N143">
         <v>9</v>
@@ -6767,7 +6914,7 @@
         <v>3</v>
       </c>
       <c r="I144">
-        <v>1101.52</v>
+        <v>1191.52</v>
       </c>
       <c r="J144">
         <v>1052.46</v>
@@ -6779,7 +6926,8 @@
         <v>1101.52</v>
       </c>
       <c r="M144">
-        <v>0.14499999999999999</v>
+        <f t="shared" si="2"/>
+        <v>0.11700000000000001</v>
       </c>
       <c r="N144">
         <v>9</v>
@@ -6823,6 +6971,7 @@
         <v>1077.6199999999999</v>
       </c>
       <c r="M145">
+        <f t="shared" si="2"/>
         <v>0.104</v>
       </c>
       <c r="N145">
@@ -6855,7 +7004,7 @@
         <v>3</v>
       </c>
       <c r="I146">
-        <v>1051.48</v>
+        <v>1151.48</v>
       </c>
       <c r="J146">
         <v>981.24</v>
@@ -6867,7 +7016,8 @@
         <v>1051.48</v>
       </c>
       <c r="M146">
-        <v>6.7000000000000004E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.14799999999999999</v>
       </c>
       <c r="N146">
         <v>9</v>
@@ -6911,6 +7061,7 @@
         <v>1164.44</v>
       </c>
       <c r="M147">
+        <f t="shared" si="2"/>
         <v>0.14599999999999999</v>
       </c>
       <c r="N147">
@@ -6943,7 +7094,7 @@
         <v>3</v>
       </c>
       <c r="I148">
-        <v>1128.04</v>
+        <v>1198.04</v>
       </c>
       <c r="J148">
         <v>1053.1210000000001</v>
@@ -6955,7 +7106,8 @@
         <v>1128.04</v>
       </c>
       <c r="M148">
-        <v>0.126</v>
+        <f t="shared" si="2"/>
+        <v>0.121</v>
       </c>
       <c r="N148">
         <v>9</v>
@@ -6987,7 +7139,7 @@
         <v>3</v>
       </c>
       <c r="I149">
-        <v>1117.28</v>
+        <v>1157.28</v>
       </c>
       <c r="J149">
         <v>1030.54</v>
@@ -6999,7 +7151,8 @@
         <v>1117.28</v>
       </c>
       <c r="M149">
-        <v>0.123</v>
+        <f t="shared" si="2"/>
+        <v>0.11</v>
       </c>
       <c r="N149">
         <v>9</v>
@@ -7031,7 +7184,7 @@
         <v>3</v>
       </c>
       <c r="I150">
-        <v>1214.96</v>
+        <v>1274.96</v>
       </c>
       <c r="J150">
         <v>1137.92</v>
@@ -7043,7 +7196,8 @@
         <v>1214.96</v>
       </c>
       <c r="M150">
-        <v>0.10630000000000001</v>
+        <f t="shared" si="2"/>
+        <v>0.107</v>
       </c>
       <c r="N150">
         <v>9</v>
@@ -7087,6 +7241,7 @@
         <v>1082.0999999999999</v>
       </c>
       <c r="M151">
+        <f t="shared" si="2"/>
         <v>0.11899999999999999</v>
       </c>
       <c r="N151">
@@ -7131,6 +7286,7 @@
         <v>258.02</v>
       </c>
       <c r="M152">
+        <f t="shared" si="2"/>
         <v>0.25800000000000001</v>
       </c>
       <c r="N152">
@@ -7175,6 +7331,7 @@
         <v>300.38</v>
       </c>
       <c r="M153">
+        <f t="shared" si="2"/>
         <v>0.17799999999999999</v>
       </c>
       <c r="N153">
@@ -7219,6 +7376,7 @@
         <v>331.52</v>
       </c>
       <c r="M154">
+        <f t="shared" si="2"/>
         <v>0.219</v>
       </c>
       <c r="N154">
@@ -7263,7 +7421,8 @@
         <v>318.64</v>
       </c>
       <c r="M155">
-        <v>0.23200000000000001</v>
+        <f t="shared" si="2"/>
+        <v>0.22500000000000001</v>
       </c>
       <c r="N155">
         <v>9</v>
@@ -7307,6 +7466,7 @@
         <v>301.22000000000003</v>
       </c>
       <c r="M156">
+        <f t="shared" si="2"/>
         <v>0.187</v>
       </c>
       <c r="N156">
@@ -7351,6 +7511,7 @@
         <v>304.64</v>
       </c>
       <c r="M157">
+        <f t="shared" si="2"/>
         <v>0.20399999999999999</v>
       </c>
       <c r="N157">
@@ -7395,7 +7556,8 @@
         <v>266.33999999999997</v>
       </c>
       <c r="M158">
-        <v>0.24399999999999999</v>
+        <f t="shared" si="2"/>
+        <v>0.24</v>
       </c>
       <c r="N158">
         <v>9</v>
@@ -7439,6 +7601,7 @@
         <v>319.08</v>
       </c>
       <c r="M159">
+        <f t="shared" si="2"/>
         <v>0.25600000000000001</v>
       </c>
       <c r="N159">
@@ -7483,7 +7646,8 @@
         <v>345.34</v>
       </c>
       <c r="M160">
-        <v>0.19800000000000001</v>
+        <f t="shared" si="2"/>
+        <v>0.17699999999999999</v>
       </c>
       <c r="N160">
         <v>9</v>
@@ -7527,6 +7691,7 @@
         <v>352.98</v>
       </c>
       <c r="M161">
+        <f t="shared" si="2"/>
         <v>0.185</v>
       </c>
       <c r="N161">
@@ -7571,6 +7736,7 @@
         <v>260.60000000000002</v>
       </c>
       <c r="M162">
+        <f t="shared" si="2"/>
         <v>0.20399999999999999</v>
       </c>
       <c r="N162">
@@ -7615,6 +7781,7 @@
         <v>227.98</v>
       </c>
       <c r="M163">
+        <f t="shared" si="2"/>
         <v>0.255</v>
       </c>
       <c r="N163">
@@ -7659,6 +7826,7 @@
         <v>297.2</v>
       </c>
       <c r="M164">
+        <f t="shared" si="2"/>
         <v>0.20300000000000001</v>
       </c>
       <c r="N164">
@@ -7703,6 +7871,7 @@
         <v>261.52</v>
       </c>
       <c r="M165">
+        <f t="shared" si="2"/>
         <v>0.20899999999999999</v>
       </c>
       <c r="N165">
@@ -7747,6 +7916,7 @@
         <v>339.74</v>
       </c>
       <c r="M166">
+        <f t="shared" si="2"/>
         <v>0.20100000000000001</v>
       </c>
       <c r="N166">
@@ -7791,6 +7961,7 @@
         <v>228.64</v>
       </c>
       <c r="M167">
+        <f t="shared" si="2"/>
         <v>0.21199999999999999</v>
       </c>
       <c r="N167">
@@ -7835,6 +8006,7 @@
         <v>334.34</v>
       </c>
       <c r="M168">
+        <f t="shared" si="2"/>
         <v>0.189</v>
       </c>
       <c r="N168">
@@ -7879,6 +8051,7 @@
         <v>279.08</v>
       </c>
       <c r="M169">
+        <f t="shared" si="2"/>
         <v>0.185</v>
       </c>
       <c r="N169">
@@ -7923,6 +8096,7 @@
         <v>257.74</v>
       </c>
       <c r="M170">
+        <f t="shared" si="2"/>
         <v>0.252</v>
       </c>
       <c r="N170">
@@ -7967,6 +8141,7 @@
         <v>265.45999999999998</v>
       </c>
       <c r="M171">
+        <f t="shared" si="2"/>
         <v>0.20300000000000001</v>
       </c>
       <c r="N171">
@@ -8011,6 +8186,7 @@
         <v>299</v>
       </c>
       <c r="M172">
+        <f t="shared" si="2"/>
         <v>0.27500000000000002</v>
       </c>
       <c r="N172">
@@ -8055,6 +8231,7 @@
         <v>292.60000000000002</v>
       </c>
       <c r="M173">
+        <f t="shared" si="2"/>
         <v>0.19700000000000001</v>
       </c>
       <c r="N173">
@@ -8099,6 +8276,7 @@
         <v>292.62</v>
       </c>
       <c r="M174">
+        <f t="shared" si="2"/>
         <v>0.19700000000000001</v>
       </c>
       <c r="N174">
@@ -8143,6 +8321,7 @@
         <v>331.78</v>
       </c>
       <c r="M175">
+        <f t="shared" si="2"/>
         <v>0.17100000000000001</v>
       </c>
       <c r="N175">
@@ -8187,6 +8366,7 @@
         <v>252.62</v>
       </c>
       <c r="M176">
+        <f t="shared" si="2"/>
         <v>0.23899999999999999</v>
       </c>
       <c r="N176">
@@ -8231,6 +8411,7 @@
         <v>378.96</v>
       </c>
       <c r="M177">
+        <f t="shared" si="2"/>
         <v>0.13100000000000001</v>
       </c>
       <c r="N177">
@@ -8263,7 +8444,7 @@
         <v>3</v>
       </c>
       <c r="I178">
-        <v>427.6</v>
+        <v>477.6</v>
       </c>
       <c r="J178">
         <v>390.64</v>
@@ -8275,7 +8456,8 @@
         <v>427.6</v>
       </c>
       <c r="M178">
-        <v>8.5999999999999993E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.182</v>
       </c>
       <c r="N178">
         <v>9</v>
@@ -8319,6 +8501,7 @@
         <v>457.2</v>
       </c>
       <c r="M179">
+        <f t="shared" si="2"/>
         <v>0.121</v>
       </c>
       <c r="N179">
@@ -8363,6 +8546,7 @@
         <v>437.44</v>
       </c>
       <c r="M180">
+        <f t="shared" si="2"/>
         <v>0.12</v>
       </c>
       <c r="N180">
@@ -8407,6 +8591,7 @@
         <v>427.46</v>
       </c>
       <c r="M181">
+        <f t="shared" si="2"/>
         <v>0.109</v>
       </c>
       <c r="N181">
@@ -8451,6 +8636,7 @@
         <v>430.22</v>
       </c>
       <c r="M182">
+        <f t="shared" si="2"/>
         <v>0.124</v>
       </c>
       <c r="N182">
@@ -8495,6 +8681,7 @@
         <v>386.78</v>
       </c>
       <c r="M183">
+        <f t="shared" si="2"/>
         <v>0.14199999999999999</v>
       </c>
       <c r="N183">
@@ -8539,6 +8726,7 @@
         <v>439.94</v>
       </c>
       <c r="M184">
+        <f t="shared" si="2"/>
         <v>0.12</v>
       </c>
       <c r="N184">
@@ -8583,6 +8771,7 @@
         <v>480.08</v>
       </c>
       <c r="M185">
+        <f t="shared" si="2"/>
         <v>0.111</v>
       </c>
       <c r="N185">
@@ -8627,6 +8816,7 @@
         <v>486.42</v>
       </c>
       <c r="M186">
+        <f t="shared" si="2"/>
         <v>0.109</v>
       </c>
       <c r="N186">
@@ -8671,6 +8861,7 @@
         <v>382.8</v>
       </c>
       <c r="M187">
+        <f t="shared" si="2"/>
         <v>0.12</v>
       </c>
       <c r="N187">
@@ -8715,6 +8906,7 @@
         <v>343.26</v>
       </c>
       <c r="M188">
+        <f t="shared" si="2"/>
         <v>0.153</v>
       </c>
       <c r="N188">
@@ -8747,7 +8939,7 @@
         <v>3</v>
       </c>
       <c r="I189">
-        <v>419.38</v>
+        <v>492.38</v>
       </c>
       <c r="J189">
         <v>377.98</v>
@@ -8759,7 +8951,8 @@
         <v>419.38</v>
       </c>
       <c r="M189">
-        <v>9.9000000000000005E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.23200000000000001</v>
       </c>
       <c r="N189">
         <v>9</v>
@@ -8791,7 +8984,7 @@
         <v>3</v>
       </c>
       <c r="I190">
-        <v>391.14</v>
+        <v>403.14</v>
       </c>
       <c r="J190">
         <v>354.7</v>
@@ -8803,7 +8996,8 @@
         <v>391.14</v>
       </c>
       <c r="M190">
-        <v>9.2999999999999999E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.12</v>
       </c>
       <c r="N190">
         <v>9</v>
@@ -8847,6 +9041,7 @@
         <v>467.58</v>
       </c>
       <c r="M191">
+        <f t="shared" si="2"/>
         <v>0.127</v>
       </c>
       <c r="N191">
@@ -8891,6 +9086,7 @@
         <v>352.44</v>
       </c>
       <c r="M192">
+        <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
       <c r="N192">
@@ -8935,6 +9131,7 @@
         <v>463.96</v>
       </c>
       <c r="M193">
+        <f t="shared" si="2"/>
         <v>0.114</v>
       </c>
       <c r="N193">
@@ -8967,7 +9164,7 @@
         <v>3</v>
       </c>
       <c r="I194">
-        <v>407.9</v>
+        <v>447.9</v>
       </c>
       <c r="J194">
         <v>379.12</v>
@@ -8979,7 +9176,8 @@
         <v>407.9</v>
       </c>
       <c r="M194">
-        <v>7.0999999999999994E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.154</v>
       </c>
       <c r="N194">
         <v>9</v>
@@ -9023,6 +9221,7 @@
         <v>377.12</v>
       </c>
       <c r="M195">
+        <f t="shared" ref="M195:M226" si="3">ROUND((I195-J195)/I195,3)</f>
         <v>0.108</v>
       </c>
       <c r="N195">
@@ -9067,6 +9266,7 @@
         <v>387.96</v>
       </c>
       <c r="M196">
+        <f t="shared" si="3"/>
         <v>0.123</v>
       </c>
       <c r="N196">
@@ -9111,6 +9311,7 @@
         <v>411.88</v>
       </c>
       <c r="M197">
+        <f t="shared" si="3"/>
         <v>0.14299999999999999</v>
       </c>
       <c r="N197">
@@ -9155,6 +9356,7 @@
         <v>418.52</v>
       </c>
       <c r="M198">
+        <f t="shared" si="3"/>
         <v>0.106</v>
       </c>
       <c r="N198">
@@ -9199,6 +9401,7 @@
         <v>416.84</v>
       </c>
       <c r="M199">
+        <f t="shared" si="3"/>
         <v>0.111</v>
       </c>
       <c r="N199">
@@ -9243,6 +9446,7 @@
         <v>465.02</v>
       </c>
       <c r="M200">
+        <f t="shared" si="3"/>
         <v>0.11899999999999999</v>
       </c>
       <c r="N200">
@@ -9287,6 +9491,7 @@
         <v>372.7</v>
       </c>
       <c r="M201">
+        <f t="shared" si="3"/>
         <v>0.11600000000000001</v>
       </c>
       <c r="N201">
@@ -9319,7 +9524,7 @@
         <v>3</v>
       </c>
       <c r="I202">
-        <v>502.08</v>
+        <v>572.08000000000004</v>
       </c>
       <c r="J202">
         <v>473.56</v>
@@ -9331,7 +9536,8 @@
         <v>502.08</v>
       </c>
       <c r="M202">
-        <v>5.7000000000000002E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.17199999999999999</v>
       </c>
       <c r="N202">
         <v>9</v>
@@ -9363,7 +9569,7 @@
         <v>3</v>
       </c>
       <c r="I203">
-        <v>559.82000000000005</v>
+        <v>659.82</v>
       </c>
       <c r="J203">
         <v>535.82000000000005</v>
@@ -9375,7 +9581,8 @@
         <v>559.82000000000005</v>
       </c>
       <c r="M203">
-        <v>4.2999999999999997E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.188</v>
       </c>
       <c r="N203">
         <v>9</v>
@@ -9407,7 +9614,7 @@
         <v>3</v>
       </c>
       <c r="I204">
-        <v>586.88</v>
+        <v>626.88</v>
       </c>
       <c r="J204">
         <v>541.12</v>
@@ -9419,7 +9626,8 @@
         <v>586.88</v>
       </c>
       <c r="M204">
-        <v>7.8E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.13700000000000001</v>
       </c>
       <c r="N204">
         <v>9</v>
@@ -9451,7 +9659,7 @@
         <v>3</v>
       </c>
       <c r="I205">
-        <v>563.79999999999995</v>
+        <v>603.79999999999995</v>
       </c>
       <c r="J205">
         <v>531.34</v>
@@ -9463,7 +9671,8 @@
         <v>563.79999999999995</v>
       </c>
       <c r="M205">
-        <v>5.8000000000000003E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.12</v>
       </c>
       <c r="N205">
         <v>9</v>
@@ -9495,7 +9704,7 @@
         <v>3</v>
       </c>
       <c r="I206">
-        <v>555.05999999999995</v>
+        <v>595.05999999999995</v>
       </c>
       <c r="J206">
         <v>512.38</v>
@@ -9507,7 +9716,8 @@
         <v>555.05999999999995</v>
       </c>
       <c r="M206">
-        <v>7.6999999999999999E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.13900000000000001</v>
       </c>
       <c r="N206">
         <v>9</v>
@@ -9539,7 +9749,7 @@
         <v>3</v>
       </c>
       <c r="I207">
-        <v>567.76</v>
+        <v>627.76</v>
       </c>
       <c r="J207">
         <v>543.05999999999995</v>
@@ -9551,7 +9761,8 @@
         <v>567.76</v>
       </c>
       <c r="M207">
-        <v>4.3999999999999997E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.13500000000000001</v>
       </c>
       <c r="N207">
         <v>9</v>
@@ -9583,7 +9794,7 @@
         <v>3</v>
       </c>
       <c r="I208">
-        <v>506.88</v>
+        <v>556.88</v>
       </c>
       <c r="J208">
         <v>464.68</v>
@@ -9595,7 +9806,8 @@
         <v>506.88</v>
       </c>
       <c r="M208">
-        <v>8.3000000000000004E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.16600000000000001</v>
       </c>
       <c r="N208">
         <v>9</v>
@@ -9627,7 +9839,7 @@
         <v>3</v>
       </c>
       <c r="I209">
-        <v>567.98</v>
+        <v>597.98</v>
       </c>
       <c r="J209">
         <v>520.52</v>
@@ -9639,7 +9851,8 @@
         <v>567.98</v>
       </c>
       <c r="M209">
-        <v>8.4000000000000005E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.13</v>
       </c>
       <c r="N209">
         <v>9</v>
@@ -9671,7 +9884,7 @@
         <v>3</v>
       </c>
       <c r="I210">
-        <v>612.74</v>
+        <v>642.74</v>
       </c>
       <c r="J210">
         <v>569.38</v>
@@ -9683,7 +9896,8 @@
         <v>612.74</v>
       </c>
       <c r="M210">
-        <v>7.0999999999999994E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.114</v>
       </c>
       <c r="N210">
         <v>9</v>
@@ -9715,7 +9929,7 @@
         <v>3</v>
       </c>
       <c r="I211">
-        <v>620.04</v>
+        <v>650.04</v>
       </c>
       <c r="J211">
         <v>583.32000000000005</v>
@@ -9727,7 +9941,8 @@
         <v>620.04</v>
       </c>
       <c r="M211">
-        <v>5.8999999999999997E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.10299999999999999</v>
       </c>
       <c r="N211">
         <v>9</v>
@@ -9759,7 +9974,7 @@
         <v>3</v>
       </c>
       <c r="I212">
-        <v>510.76</v>
+        <v>560.76</v>
       </c>
       <c r="J212">
         <v>488.68</v>
@@ -9771,7 +9986,8 @@
         <v>510.76</v>
       </c>
       <c r="M212">
-        <v>4.2999999999999997E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.129</v>
       </c>
       <c r="N212">
         <v>9</v>
@@ -9803,7 +10019,7 @@
         <v>3</v>
       </c>
       <c r="I213">
-        <v>466.8</v>
+        <v>526.79999999999995</v>
       </c>
       <c r="J213">
         <v>426.64</v>
@@ -9815,7 +10031,8 @@
         <v>466.8</v>
       </c>
       <c r="M213">
-        <v>8.5999999999999993E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.19</v>
       </c>
       <c r="N213">
         <v>9</v>
@@ -9847,7 +10064,7 @@
         <v>3</v>
       </c>
       <c r="I214">
-        <v>556.14</v>
+        <v>596.14</v>
       </c>
       <c r="J214">
         <v>527.79999999999995</v>
@@ -9859,7 +10076,8 @@
         <v>556.14</v>
       </c>
       <c r="M214">
-        <v>5.0999999999999997E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.115</v>
       </c>
       <c r="N214">
         <v>9</v>
@@ -9891,7 +10109,7 @@
         <v>3</v>
       </c>
       <c r="I215">
-        <v>519.32000000000005</v>
+        <v>589.32000000000005</v>
       </c>
       <c r="J215">
         <v>493.2</v>
@@ -9903,7 +10121,8 @@
         <v>519.32000000000005</v>
       </c>
       <c r="M215">
-        <v>0.05</v>
+        <f t="shared" si="3"/>
+        <v>0.16300000000000001</v>
       </c>
       <c r="N215">
         <v>9</v>
@@ -9935,7 +10154,7 @@
         <v>3</v>
       </c>
       <c r="I216">
-        <v>597.12</v>
+        <v>657.12</v>
       </c>
       <c r="J216">
         <v>571.14</v>
@@ -9947,7 +10166,8 @@
         <v>597.12</v>
       </c>
       <c r="M216">
-        <v>4.3999999999999997E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.13100000000000001</v>
       </c>
       <c r="N216">
         <v>9</v>
@@ -9979,7 +10199,7 @@
         <v>3</v>
       </c>
       <c r="I217">
-        <v>476.84</v>
+        <v>526.84</v>
       </c>
       <c r="J217">
         <v>451.92</v>
@@ -9991,7 +10211,8 @@
         <v>476.84</v>
       </c>
       <c r="M217">
-        <v>5.1999999999999998E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.14199999999999999</v>
       </c>
       <c r="N217">
         <v>9</v>
@@ -10023,7 +10244,7 @@
         <v>3</v>
       </c>
       <c r="I218">
-        <v>600.05999999999995</v>
+        <v>640.05999999999995</v>
       </c>
       <c r="J218">
         <v>559.08000000000004</v>
@@ -10035,7 +10256,8 @@
         <v>600.05999999999995</v>
       </c>
       <c r="M218">
-        <v>6.8000000000000005E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.127</v>
       </c>
       <c r="N218">
         <v>9</v>
@@ -10067,7 +10289,7 @@
         <v>3</v>
       </c>
       <c r="I219">
-        <v>545.1</v>
+        <v>605.1</v>
       </c>
       <c r="J219">
         <v>537</v>
@@ -10079,7 +10301,8 @@
         <v>545.1</v>
       </c>
       <c r="M219">
-        <v>1.4999999999999999E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.113</v>
       </c>
       <c r="N219">
         <v>9</v>
@@ -10111,7 +10334,7 @@
         <v>3</v>
       </c>
       <c r="I220">
-        <v>504.56</v>
+        <v>574.55999999999995</v>
       </c>
       <c r="J220">
         <v>477.96</v>
@@ -10123,7 +10346,8 @@
         <v>504.56</v>
       </c>
       <c r="M220">
-        <v>5.2999999999999999E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.16800000000000001</v>
       </c>
       <c r="N220">
         <v>9</v>
@@ -10155,7 +10379,7 @@
         <v>3</v>
       </c>
       <c r="I221">
-        <v>515.05999999999995</v>
+        <v>576.05999999999995</v>
       </c>
       <c r="J221">
         <v>497.52</v>
@@ -10167,7 +10391,8 @@
         <v>515.05999999999995</v>
       </c>
       <c r="M221">
-        <v>3.4000000000000002E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.13600000000000001</v>
       </c>
       <c r="N221">
         <v>9</v>
@@ -10199,7 +10424,7 @@
         <v>3</v>
       </c>
       <c r="I222">
-        <v>536.66</v>
+        <v>566.66</v>
       </c>
       <c r="J222">
         <v>487.5</v>
@@ -10211,7 +10436,8 @@
         <v>536.66</v>
       </c>
       <c r="M222">
-        <v>9.1999999999999998E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.14000000000000001</v>
       </c>
       <c r="N222">
         <v>9</v>
@@ -10243,7 +10469,7 @@
         <v>3</v>
       </c>
       <c r="I223">
-        <v>549.66</v>
+        <v>589.66</v>
       </c>
       <c r="J223">
         <v>520.08000000000004</v>
@@ -10255,7 +10481,8 @@
         <v>549.66</v>
       </c>
       <c r="M223">
-        <v>5.3999999999999999E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.11799999999999999</v>
       </c>
       <c r="N223">
         <v>9</v>
@@ -10287,7 +10514,7 @@
         <v>3</v>
       </c>
       <c r="I224">
-        <v>545.1</v>
+        <v>575.1</v>
       </c>
       <c r="J224">
         <v>507.32</v>
@@ -10299,7 +10526,8 @@
         <v>545.1</v>
       </c>
       <c r="M224">
-        <v>6.9000000000000006E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.11799999999999999</v>
       </c>
       <c r="N224">
         <v>9</v>
@@ -10331,7 +10559,7 @@
         <v>3</v>
       </c>
       <c r="I225">
-        <v>594.9</v>
+        <v>664.9</v>
       </c>
       <c r="J225">
         <v>575.44000000000005</v>
@@ -10343,7 +10571,8 @@
         <v>594.9</v>
       </c>
       <c r="M225">
-        <v>3.3000000000000002E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.13500000000000001</v>
       </c>
       <c r="N225">
         <v>9</v>
@@ -10375,7 +10604,7 @@
         <v>3</v>
       </c>
       <c r="I226">
-        <v>500.32</v>
+        <v>550.32000000000005</v>
       </c>
       <c r="J226">
         <v>463.76</v>
@@ -10387,7 +10616,8 @@
         <v>500.32</v>
       </c>
       <c r="M226">
-        <v>7.2999999999999995E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.157</v>
       </c>
       <c r="N226">
         <v>9</v>
